--- a/reports/telegram/aegis_daily_2026-08-10.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-10.xlsx
@@ -795,12 +795,8 @@
       <c r="J2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="n">
         <v>79.3</v>
       </c>
@@ -822,7 +818,7 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 57% · band HOLD · 14d left · → BUY</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -909,7 +905,7 @@
       </c>
       <c r="AU2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -954,12 +950,8 @@
       <c r="J3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="n">
         <v>86.5</v>
       </c>
@@ -981,7 +973,7 @@
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.7%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+          <t>🟢 BUY (Δ-3.7%) · Rank #2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr"/>
@@ -1066,7 +1058,7 @@
       </c>
       <c r="AU3" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1109,8 @@
       <c r="J4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="K4" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
       <c r="M4" s="7" t="n">
         <v>67.5</v>
       </c>
@@ -1144,7 +1132,7 @@
       </c>
       <c r="R4" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 3→3 · Conf 47% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #3 · Conf 47% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
@@ -1233,7 +1221,7 @@
       </c>
       <c r="AU4" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1272,8 @@
       <c r="J5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K5" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="n">
         <v>78.40000000000001</v>
       </c>
@@ -1311,7 +1295,7 @@
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
@@ -1400,7 +1384,7 @@
       </c>
       <c r="AU5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1435,8 @@
       <c r="J6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K6" s="7" t="inlineStr"/>
+      <c r="L6" s="7" t="inlineStr"/>
       <c r="M6" s="7" t="n">
         <v>76</v>
       </c>
@@ -1478,7 +1458,7 @@
       </c>
       <c r="R6" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
@@ -1567,7 +1547,7 @@
       </c>
       <c r="AU6" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1598,8 @@
       <c r="J7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr"/>
       <c r="M7" s="7" t="n">
         <v>66.3</v>
       </c>
@@ -1645,7 +1621,7 @@
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 6→6 · Conf 51% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #6 · Conf 51% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S7" s="7" t="inlineStr"/>
@@ -1730,7 +1706,7 @@
       </c>
       <c r="AU7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1757,8 @@
       <c r="J8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="K8" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr"/>
       <c r="M8" s="7" t="n">
         <v>83.5</v>
       </c>
@@ -1808,7 +1780,7 @@
       </c>
       <c r="R8" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 7→7 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #7 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S8" s="7" t="inlineStr"/>
@@ -1893,7 +1865,7 @@
       </c>
       <c r="AU8" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1916,8 @@
       <c r="J9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="K9" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
       <c r="M9" s="7" t="n">
         <v>79.5</v>
       </c>
@@ -1971,7 +1939,7 @@
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
@@ -2060,7 +2028,7 @@
       </c>
       <c r="AU9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2079,8 @@
       <c r="J10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="K10" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="L10" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr"/>
       <c r="M10" s="7" t="n">
         <v>84.09999999999999</v>
       </c>
@@ -2138,7 +2102,7 @@
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 9→9 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #9 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
@@ -2227,7 +2191,7 @@
       </c>
       <c r="AU10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -2278,12 +2242,8 @@
       <c r="J11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="K11" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
       <c r="M11" s="7" t="n">
         <v>76.2</v>
       </c>
@@ -2305,7 +2265,7 @@
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
@@ -2394,7 +2354,7 @@
       </c>
       <c r="AU11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2405,8 @@
       <c r="J12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="K12" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K12" s="7" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr"/>
       <c r="M12" s="7" t="n">
         <v>52.5</v>
       </c>
@@ -2472,7 +2428,7 @@
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 11→11 · Conf 29% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #11 · Conf 29% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
@@ -2561,7 +2517,7 @@
       </c>
       <c r="AU12" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -2612,12 +2568,8 @@
       <c r="J13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="K13" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="L13" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
       <c r="M13" s="7" t="n">
         <v>52.6</v>
       </c>
@@ -2639,7 +2591,7 @@
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 12→12 · Conf 31% · band EXIT · 58d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #12 · Conf 31% · band EXIT · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
@@ -2728,7 +2680,7 @@
       </c>
       <c r="AU13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2731,8 @@
       <c r="J14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="K14" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr"/>
       <c r="M14" s="7" t="n">
         <v>52.8</v>
       </c>
@@ -2806,7 +2754,7 @@
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 13→13 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #13 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S14" s="7" t="inlineStr"/>
@@ -2891,7 +2839,7 @@
       </c>
       <c r="AU14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -2942,12 +2890,8 @@
       <c r="J15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="K15" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="L15" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
       <c r="M15" s="7" t="n">
         <v>52.8</v>
       </c>
@@ -2969,7 +2913,7 @@
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 14→14 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #14 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S15" s="7" t="inlineStr"/>
@@ -3054,7 +2998,7 @@
       </c>
       <c r="AU15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -3105,12 +3049,8 @@
       <c r="J16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="K16" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="L16" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr"/>
       <c r="M16" s="7" t="n">
         <v>52.5</v>
       </c>
@@ -3132,7 +3072,7 @@
       </c>
       <c r="R16" s="7" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 15→15 · Conf 28% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #15 · Conf 28% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S16" s="7" t="inlineStr"/>
@@ -3217,7 +3157,7 @@
       </c>
       <c r="AU16" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3310,7 @@
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3463,7 @@
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3620,7 @@
       </c>
       <c r="AU19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3777,7 @@
       </c>
       <c r="AU20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3934,7 @@
       </c>
       <c r="AU21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4091,7 @@
       </c>
       <c r="AU22" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4244,7 @@
       </c>
       <c r="AU23" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4401,7 @@
       </c>
       <c r="AU24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4554,7 @@
       </c>
       <c r="AU25" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
@@ -4771,7 +4711,7 @@
       </c>
       <c r="AU26" s="5" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
     </row>
